--- a/outputs/tables/posrri_results.xlsx
+++ b/outputs/tables/posrri_results.xlsx
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.93405530452418</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="C2" t="n">
         <v>88.33333333333333</v>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88.15630755118589</v>
+        <v>80</v>
       </c>
       <c r="C3" t="n">
         <v>81.00000000000001</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.43952714026133</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="C4" t="n">
         <v>88</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.57455978868064</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
         <v>97</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.43936410087769</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="C6" t="n">
         <v>91</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.34277051867221</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="C7" t="n">
         <v>83.66666666666666</v>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.5027021107075</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="C8" t="n">
         <v>88.33333333333333</v>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.30657908308432</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="C9" t="n">
         <v>96.66666666666667</v>
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.62158004932841</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
         <v>83.33333333333333</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44.39432783807527</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="C11" t="n">
         <v>89.33333333333333</v>

--- a/outputs/tables/posrri_results.xlsx
+++ b/outputs/tables/posrri_results.xlsx
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.33333333333334</v>
+        <v>69.93405530452418</v>
       </c>
       <c r="C2" t="n">
         <v>88.33333333333333</v>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>88.15630755118589</v>
       </c>
       <c r="C3" t="n">
         <v>81.00000000000001</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66.66666666666667</v>
+        <v>67.43952714026133</v>
       </c>
       <c r="C4" t="n">
         <v>88</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>41.57455978868064</v>
       </c>
       <c r="C5" t="n">
         <v>97</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.33333333333333</v>
+        <v>12.43936410087769</v>
       </c>
       <c r="C6" t="n">
         <v>91</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.33333333333334</v>
+        <v>23.34277051867221</v>
       </c>
       <c r="C7" t="n">
         <v>83.66666666666666</v>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.66666666666667</v>
+        <v>35.5027021107075</v>
       </c>
       <c r="C8" t="n">
         <v>88.33333333333333</v>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.33333333333334</v>
+        <v>32.30657908308432</v>
       </c>
       <c r="C9" t="n">
         <v>96.66666666666667</v>
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>41.62158004932841</v>
       </c>
       <c r="C10" t="n">
         <v>83.33333333333333</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46.66666666666666</v>
+        <v>44.39432783807527</v>
       </c>
       <c r="C11" t="n">
         <v>89.33333333333333</v>

--- a/outputs/tables/posrri_results.xlsx
+++ b/outputs/tables/posrri_results.xlsx
@@ -23,6 +23,10 @@
     <sheet name="13_sensitivity_domains" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="14_sensitivity_pillars" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="15_benchmark_0_100" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16_survey_likert" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17_survey_frequencies" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="18_survey_text" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="19_survey_alpha_items" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +691,51 @@
       <c r="C17" t="inlineStr">
         <is>
           <t>p = 2.93e-05; 5 domains change rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Survey respondents</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7 Likert, 5 coded, 3 free-text items</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cronbach's alpha (7-item scale)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.8152</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>good; 50 complete cases, 0 excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mean Likert score</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>highest q4, lowest q9</t>
         </is>
       </c>
     </row>
@@ -8358,6 +8407,1108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_missing</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>q1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>q3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pct_1_2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>pct_4_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>q1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Plan would work in a Tier 2 spill</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7866228513106404</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>q3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Own roles and responsibilities are clear</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8992059989632124</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>q4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Response equipment is adequate</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9035079029052513</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" t="n">
+        <v>56.00000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>q5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Inter-agency coordination is effective</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.026386568382061</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>q8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Confidence in the notification chain</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9981615754036243</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>32</v>
+      </c>
+      <c r="M6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>q9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Funding for preparedness is adequate</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9278018789216868</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>q10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lessons from incidents are acted upon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7583548251421142</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>54</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_of_valid</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>n_valid</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>n_missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>q2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aware of designated On-Scene Commander</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>q2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Aware of designated On-Scene Commander</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>q2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aware of designated On-Scene Commander</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>q6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Given access to the contingency plan</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>q6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Given access to the contingency plan</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>q6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Given access to the contingency plan</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" t="n">
+        <v>34</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>q7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Frequency of exercise participation</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30.23255813953488</v>
+      </c>
+      <c r="G8" t="n">
+        <v>43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>q7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Frequency of exercise participation</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>34.88372093023256</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>q7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Frequency of exercise participation</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30.23255813953488</v>
+      </c>
+      <c r="G10" t="n">
+        <v>43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>q7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Frequency of exercise participation</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.651162790697675</v>
+      </c>
+      <c r="G11" t="n">
+        <v>43</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>q13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Years of relevant experience</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Less than 2 years</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>q13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Years of relevant experience</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2-5 years</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F13" t="n">
+        <v>44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>q13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Years of relevant experience</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>q13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Years of relevant experience</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>More than 10 years</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>q14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Formal OPRC training received</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>48</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>q14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Formal OPRC training received</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>26</v>
+      </c>
+      <c r="F17" t="n">
+        <v>52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_answered</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_blank</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_answered</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>n_distinct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>most_common</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>q11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Greatest barrier (free text)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unclear lines of authority (10); Equipment is not maintained (8); No dedicated budget (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>q12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Most valuable single change (free text)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Run a full-scale annual exercise (11); Appoint a permanent on-scene commander (10); Publish the plan to all terminals (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>q15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Organisation (free text)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Terminal operator (10); Fisheries department (8); Coast guard (8)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9997,6 +11148,246 @@
         <is>
           <t>Independent audit or external peer review of preparedness</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>item_total_r</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>alpha_if_deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>q1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Plan would work in a Tier 2 spill</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7866228513106404</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6746395812294175</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7734506742370474</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>q3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Own roles and responsibilities are clear</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8992059989632124</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.510368406187348</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7981333333333333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>q4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Response equipment is adequate</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9035079029052513</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5588007800662219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7898923937423695</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>q5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Inter-agency coordination is effective</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.026386568382061</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6120143818795296</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7804175314369429</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>q8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Confidence in the notification chain</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9981615754036243</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5894146360065474</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.784620895522388</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>q9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Funding for preparedness is adequate</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9278018789216868</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5316176181231257</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7946992864424056</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>q10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lessons from incidents are acted upon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7583548251421142</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4164860157789656</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8116054951814639</v>
       </c>
     </row>
   </sheetData>
